--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:17</t>
+    <t xml:space="preserve">2026-09-09 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:12</t>
+    <t xml:space="preserve">2026-09-17 14:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:08</t>
+    <t xml:space="preserve">2026-09-23 12:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:37</t>
+    <t xml:space="preserve">2026-10-02 14:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:54</t>
+    <t xml:space="preserve">2026-10-05 11:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -637,7 +637,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1111165.12</v>
+        <v>1111165.13</v>
       </c>
     </row>
     <row r="3">
@@ -654,7 +654,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1074141.12</v>
+        <v>1074141.13</v>
       </c>
     </row>
     <row r="4">
@@ -688,7 +688,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>949489.12</v>
+        <v>949489.13</v>
       </c>
     </row>
     <row r="6">
@@ -841,7 +841,7 @@
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>532966.62</v>
+        <v>532966.63</v>
       </c>
     </row>
     <row r="15">
@@ -1062,7 +1062,7 @@
         <v>2023</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>426741.12</v>
+        <v>426741.13</v>
       </c>
     </row>
     <row r="28">
